--- a/descartes.xlsx
+++ b/descartes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emporio\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emporio\Desktop\DashboardDescartes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A206E662-15F9-40A4-94AA-965A085B0091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E44B7BFE-F241-487D-B82F-A8F562DD32E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="643">
   <si>
     <t>Dia</t>
   </si>
@@ -1436,6 +1436,519 @@
   </si>
   <si>
     <t xml:space="preserve">Ana vitoria </t>
+  </si>
+  <si>
+    <t>07:52:10</t>
+  </si>
+  <si>
+    <t>07:52:23</t>
+  </si>
+  <si>
+    <t>07:52:46</t>
+  </si>
+  <si>
+    <t>08:31:38</t>
+  </si>
+  <si>
+    <t>4598</t>
+  </si>
+  <si>
+    <t>PIPOCA DOCE</t>
+  </si>
+  <si>
+    <t>12:24:32</t>
+  </si>
+  <si>
+    <t>12:24:39</t>
+  </si>
+  <si>
+    <t>12:24:53</t>
+  </si>
+  <si>
+    <t>13:44:12</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>07:07:26</t>
+  </si>
+  <si>
+    <t>07:08:23</t>
+  </si>
+  <si>
+    <t>07:08:30</t>
+  </si>
+  <si>
+    <t>07:08:35</t>
+  </si>
+  <si>
+    <t>08:12:08</t>
+  </si>
+  <si>
+    <t>08:13:15</t>
+  </si>
+  <si>
+    <t>08:13:35</t>
+  </si>
+  <si>
+    <t>08:17:43</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>BOLO DE CHOCOLATE FITA</t>
+  </si>
+  <si>
+    <t>08:18:02</t>
+  </si>
+  <si>
+    <t>08:18:16</t>
+  </si>
+  <si>
+    <t>08:18:27</t>
+  </si>
+  <si>
+    <t>10:16:09</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PIZZA DA CASA UNIDADE</t>
+  </si>
+  <si>
+    <t>10:45:35</t>
+  </si>
+  <si>
+    <t>11:55:57</t>
+  </si>
+  <si>
+    <t>11:56:55</t>
+  </si>
+  <si>
+    <t>11:57:18</t>
+  </si>
+  <si>
+    <t>11:58:25</t>
+  </si>
+  <si>
+    <t>12:38:09</t>
+  </si>
+  <si>
+    <t>12:41:04</t>
+  </si>
+  <si>
+    <t>12:41:27</t>
+  </si>
+  <si>
+    <t>12:42:25</t>
+  </si>
+  <si>
+    <t>12:53:24</t>
+  </si>
+  <si>
+    <t>12:53:31</t>
+  </si>
+  <si>
+    <t>12:53:38</t>
+  </si>
+  <si>
+    <t>13:14:58</t>
+  </si>
+  <si>
+    <t>18:15:39</t>
+  </si>
+  <si>
+    <t>18:16:49</t>
+  </si>
+  <si>
+    <t>18:24:52</t>
+  </si>
+  <si>
+    <t>20:31:35</t>
+  </si>
+  <si>
+    <t>20:38:02</t>
+  </si>
+  <si>
+    <t>664</t>
+  </si>
+  <si>
+    <t>BOLO LARANJA GR</t>
+  </si>
+  <si>
+    <t>20:38:29</t>
+  </si>
+  <si>
+    <t>20:55:28</t>
+  </si>
+  <si>
+    <t>21:32:12</t>
+  </si>
+  <si>
+    <t>21:32:18</t>
+  </si>
+  <si>
+    <t>21:35:44</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>06:59:18</t>
+  </si>
+  <si>
+    <t>11:45:52</t>
+  </si>
+  <si>
+    <t>3919</t>
+  </si>
+  <si>
+    <t>MADELEINE</t>
+  </si>
+  <si>
+    <t>11:46:29</t>
+  </si>
+  <si>
+    <t>631</t>
+  </si>
+  <si>
+    <t>BRIOCHE SIMPLES</t>
+  </si>
+  <si>
+    <t>11:46:51</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>PUDIM PQ</t>
+  </si>
+  <si>
+    <t>21:54:26</t>
+  </si>
+  <si>
+    <t>21:55:02</t>
+  </si>
+  <si>
+    <t>21:56:29</t>
+  </si>
+  <si>
+    <t>925</t>
+  </si>
+  <si>
+    <t>BOLO DE POTE</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>06:46:15</t>
+  </si>
+  <si>
+    <t>06:46:25</t>
+  </si>
+  <si>
+    <t>06:46:43</t>
+  </si>
+  <si>
+    <t>06:51:01</t>
+  </si>
+  <si>
+    <t>06:51:11</t>
+  </si>
+  <si>
+    <t>2543</t>
+  </si>
+  <si>
+    <t>BOLO RED VELVET KG</t>
+  </si>
+  <si>
+    <t>06:53:45</t>
+  </si>
+  <si>
+    <t>06:54:05</t>
+  </si>
+  <si>
+    <t>12:13:19</t>
+  </si>
+  <si>
+    <t>3156</t>
+  </si>
+  <si>
+    <t>PALMIER UND</t>
+  </si>
+  <si>
+    <t>21:10:21</t>
+  </si>
+  <si>
+    <t>21:10:30</t>
+  </si>
+  <si>
+    <t>21:10:38</t>
+  </si>
+  <si>
+    <t>21:10:50</t>
+  </si>
+  <si>
+    <t>21:11:17</t>
+  </si>
+  <si>
+    <t>21:12:14</t>
+  </si>
+  <si>
+    <t>21:20:38</t>
+  </si>
+  <si>
+    <t>21:50:48</t>
+  </si>
+  <si>
+    <t>21:50:58</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>07:36:34</t>
+  </si>
+  <si>
+    <t>08:47:55</t>
+  </si>
+  <si>
+    <t>08:48:19</t>
+  </si>
+  <si>
+    <t>08:48:49</t>
+  </si>
+  <si>
+    <t>12:05:40</t>
+  </si>
+  <si>
+    <t>12:05:55</t>
+  </si>
+  <si>
+    <t>12:06:07</t>
+  </si>
+  <si>
+    <t>12:06:12</t>
+  </si>
+  <si>
+    <t>21:16:40</t>
+  </si>
+  <si>
+    <t>21:23:05</t>
+  </si>
+  <si>
+    <t>21:23:29</t>
+  </si>
+  <si>
+    <t>21:23:39</t>
+  </si>
+  <si>
+    <t>21:24:07</t>
+  </si>
+  <si>
+    <t>21:24:31</t>
+  </si>
+  <si>
+    <t>21:25:32</t>
+  </si>
+  <si>
+    <t>21:25:39</t>
+  </si>
+  <si>
+    <t>21:26:13</t>
+  </si>
+  <si>
+    <t>21:27:04</t>
+  </si>
+  <si>
+    <t>21:27:08</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>07:09:05</t>
+  </si>
+  <si>
+    <t>07:09:13</t>
+  </si>
+  <si>
+    <t>07:10:02</t>
+  </si>
+  <si>
+    <t>07:10:22</t>
+  </si>
+  <si>
+    <t>07:11:16</t>
+  </si>
+  <si>
+    <t>21:22:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Clara </t>
+  </si>
+  <si>
+    <t>21:23:00</t>
+  </si>
+  <si>
+    <t>21:23:12</t>
+  </si>
+  <si>
+    <t>21:23:23</t>
+  </si>
+  <si>
+    <t>21:24:53</t>
+  </si>
+  <si>
+    <t>21:25:04</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>COOKIE DE NUTELLA  FATIA</t>
+  </si>
+  <si>
+    <t>21:25:25</t>
+  </si>
+  <si>
+    <t>22:02:58</t>
+  </si>
+  <si>
+    <t>22:03:03</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>07:21:34</t>
+  </si>
+  <si>
+    <t>Erick Moreno</t>
+  </si>
+  <si>
+    <t>07:40:30</t>
+  </si>
+  <si>
+    <t>07:43:18</t>
+  </si>
+  <si>
+    <t>07:44:31</t>
+  </si>
+  <si>
+    <t>07:47:50</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>PAO SEMI ITALIANO RECHEADO UN</t>
+  </si>
+  <si>
+    <t>07:49:28</t>
+  </si>
+  <si>
+    <t>07:50:12</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>BOLO FITA  SABORES</t>
+  </si>
+  <si>
+    <t>11:16:55</t>
+  </si>
+  <si>
+    <t>4129</t>
+  </si>
+  <si>
+    <t>FOCACCIA SIMPLES</t>
+  </si>
+  <si>
+    <t>11:18:34</t>
+  </si>
+  <si>
+    <t>11:19:29</t>
+  </si>
+  <si>
+    <t>12:44:44</t>
+  </si>
+  <si>
+    <t>3248</t>
+  </si>
+  <si>
+    <t>DOCES  FOLHADOS</t>
+  </si>
+  <si>
+    <t>12:47:12</t>
+  </si>
+  <si>
+    <t>13:10:28</t>
+  </si>
+  <si>
+    <t>4596</t>
+  </si>
+  <si>
+    <t>BISNAGUINHA</t>
+  </si>
+  <si>
+    <t>22:07:40</t>
+  </si>
+  <si>
+    <t>22:07:46</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>06:33:15</t>
+  </si>
+  <si>
+    <t>06:33:27</t>
+  </si>
+  <si>
+    <t>07:10:10</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>BROA DE MILHO</t>
+  </si>
+  <si>
+    <t>07:10:26</t>
+  </si>
+  <si>
+    <t>07:10:35</t>
+  </si>
+  <si>
+    <t>08:38:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Ferreira </t>
+  </si>
+  <si>
+    <t>08:38:44</t>
+  </si>
+  <si>
+    <t>12:33:39</t>
+  </si>
+  <si>
+    <t>12:33:47</t>
+  </si>
+  <si>
+    <t>12:33:57</t>
+  </si>
+  <si>
+    <t>12:42:15</t>
+  </si>
+  <si>
+    <t>13:04:05</t>
   </si>
 </sst>
 </file>
@@ -1491,8 +2004,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D11C0AE7-B341-4FFA-B5B2-4E7ADCBC7916}" name="Tabela1" displayName="Tabela1" ref="A1:H251" totalsRowShown="0">
-  <autoFilter ref="A1:H251" xr:uid="{D11C0AE7-B341-4FFA-B5B2-4E7ADCBC7916}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D11C0AE7-B341-4FFA-B5B2-4E7ADCBC7916}" name="Tabela1" displayName="Tabela1" ref="A1:H379" totalsRowShown="0">
+  <autoFilter ref="A1:H379" xr:uid="{D11C0AE7-B341-4FFA-B5B2-4E7ADCBC7916}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{7FC9670E-2AE6-4EBC-BB84-70A017D53802}" name="Dia"/>
     <tableColumn id="2" xr3:uid="{4F0C70A2-06E8-46F9-8B1C-D5C2ECA1A465}" name="Hora"/>
@@ -1804,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.28515625" customWidth="1"/>
@@ -8341,6 +8854,3334 @@
         <v>471</v>
       </c>
     </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>469</v>
+      </c>
+      <c r="B252" t="s">
+        <v>472</v>
+      </c>
+      <c r="C252" t="s">
+        <v>393</v>
+      </c>
+      <c r="D252" t="s">
+        <v>394</v>
+      </c>
+      <c r="E252">
+        <v>14.9</v>
+      </c>
+      <c r="F252">
+        <v>1</v>
+      </c>
+      <c r="G252" t="s">
+        <v>10</v>
+      </c>
+      <c r="H252" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>469</v>
+      </c>
+      <c r="B253" t="s">
+        <v>473</v>
+      </c>
+      <c r="C253" t="s">
+        <v>15</v>
+      </c>
+      <c r="D253" t="s">
+        <v>16</v>
+      </c>
+      <c r="E253">
+        <v>29.8</v>
+      </c>
+      <c r="F253">
+        <v>2</v>
+      </c>
+      <c r="G253" t="s">
+        <v>10</v>
+      </c>
+      <c r="H253" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>469</v>
+      </c>
+      <c r="B254" t="s">
+        <v>474</v>
+      </c>
+      <c r="C254" t="s">
+        <v>125</v>
+      </c>
+      <c r="D254" t="s">
+        <v>126</v>
+      </c>
+      <c r="E254">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="F254">
+        <v>4</v>
+      </c>
+      <c r="G254" t="s">
+        <v>10</v>
+      </c>
+      <c r="H254" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>469</v>
+      </c>
+      <c r="B255" t="s">
+        <v>475</v>
+      </c>
+      <c r="C255" t="s">
+        <v>476</v>
+      </c>
+      <c r="D255" t="s">
+        <v>477</v>
+      </c>
+      <c r="E255">
+        <v>9.9</v>
+      </c>
+      <c r="F255">
+        <v>1</v>
+      </c>
+      <c r="G255" t="s">
+        <v>10</v>
+      </c>
+      <c r="H255" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>469</v>
+      </c>
+      <c r="B256" t="s">
+        <v>478</v>
+      </c>
+      <c r="C256" t="s">
+        <v>8</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256">
+        <v>39.6</v>
+      </c>
+      <c r="F256">
+        <v>4</v>
+      </c>
+      <c r="G256" t="s">
+        <v>10</v>
+      </c>
+      <c r="H256" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>469</v>
+      </c>
+      <c r="B257" t="s">
+        <v>479</v>
+      </c>
+      <c r="C257" t="s">
+        <v>17</v>
+      </c>
+      <c r="D257" t="s">
+        <v>18</v>
+      </c>
+      <c r="E257">
+        <v>26.7</v>
+      </c>
+      <c r="F257">
+        <v>3</v>
+      </c>
+      <c r="G257" t="s">
+        <v>10</v>
+      </c>
+      <c r="H257" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>469</v>
+      </c>
+      <c r="B258" t="s">
+        <v>480</v>
+      </c>
+      <c r="C258" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258">
+        <v>26.7</v>
+      </c>
+      <c r="F258">
+        <v>3</v>
+      </c>
+      <c r="G258" t="s">
+        <v>10</v>
+      </c>
+      <c r="H258" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>469</v>
+      </c>
+      <c r="B259" t="s">
+        <v>481</v>
+      </c>
+      <c r="C259" t="s">
+        <v>36</v>
+      </c>
+      <c r="D259" t="s">
+        <v>37</v>
+      </c>
+      <c r="E259">
+        <v>39.53</v>
+      </c>
+      <c r="F259">
+        <v>0.66</v>
+      </c>
+      <c r="G259" t="s">
+        <v>10</v>
+      </c>
+      <c r="H259" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>482</v>
+      </c>
+      <c r="B260" t="s">
+        <v>483</v>
+      </c>
+      <c r="C260" t="s">
+        <v>361</v>
+      </c>
+      <c r="D260" t="s">
+        <v>362</v>
+      </c>
+      <c r="E260">
+        <v>89.5</v>
+      </c>
+      <c r="F260">
+        <v>5</v>
+      </c>
+      <c r="G260" t="s">
+        <v>35</v>
+      </c>
+      <c r="H260" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>482</v>
+      </c>
+      <c r="B261" t="s">
+        <v>484</v>
+      </c>
+      <c r="C261" t="s">
+        <v>50</v>
+      </c>
+      <c r="D261" t="s">
+        <v>51</v>
+      </c>
+      <c r="E261">
+        <v>12.9</v>
+      </c>
+      <c r="F261">
+        <v>1</v>
+      </c>
+      <c r="G261" t="s">
+        <v>35</v>
+      </c>
+      <c r="H261" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>482</v>
+      </c>
+      <c r="B262" t="s">
+        <v>485</v>
+      </c>
+      <c r="C262" t="s">
+        <v>50</v>
+      </c>
+      <c r="D262" t="s">
+        <v>51</v>
+      </c>
+      <c r="E262">
+        <v>12.9</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+      <c r="G262" t="s">
+        <v>35</v>
+      </c>
+      <c r="H262" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>482</v>
+      </c>
+      <c r="B263" t="s">
+        <v>486</v>
+      </c>
+      <c r="C263" t="s">
+        <v>476</v>
+      </c>
+      <c r="D263" t="s">
+        <v>477</v>
+      </c>
+      <c r="E263">
+        <v>39.6</v>
+      </c>
+      <c r="F263">
+        <v>4</v>
+      </c>
+      <c r="G263" t="s">
+        <v>35</v>
+      </c>
+      <c r="H263" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>482</v>
+      </c>
+      <c r="B264" t="s">
+        <v>487</v>
+      </c>
+      <c r="C264" t="s">
+        <v>129</v>
+      </c>
+      <c r="D264" t="s">
+        <v>130</v>
+      </c>
+      <c r="E264">
+        <v>51.6</v>
+      </c>
+      <c r="F264">
+        <v>4</v>
+      </c>
+      <c r="G264" t="s">
+        <v>35</v>
+      </c>
+      <c r="H264" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>482</v>
+      </c>
+      <c r="B265" t="s">
+        <v>488</v>
+      </c>
+      <c r="C265" t="s">
+        <v>27</v>
+      </c>
+      <c r="D265" t="s">
+        <v>28</v>
+      </c>
+      <c r="E265">
+        <v>411.44</v>
+      </c>
+      <c r="F265">
+        <v>5.8860000000000001</v>
+      </c>
+      <c r="G265" t="s">
+        <v>35</v>
+      </c>
+      <c r="H265" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>482</v>
+      </c>
+      <c r="B266" t="s">
+        <v>489</v>
+      </c>
+      <c r="C266" t="s">
+        <v>95</v>
+      </c>
+      <c r="D266" t="s">
+        <v>96</v>
+      </c>
+      <c r="E266">
+        <v>14.37</v>
+      </c>
+      <c r="F266">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="G266" t="s">
+        <v>35</v>
+      </c>
+      <c r="H266" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>482</v>
+      </c>
+      <c r="B267" t="s">
+        <v>490</v>
+      </c>
+      <c r="C267" t="s">
+        <v>491</v>
+      </c>
+      <c r="D267" t="s">
+        <v>492</v>
+      </c>
+      <c r="E267">
+        <v>95.12</v>
+      </c>
+      <c r="F267">
+        <v>1.5880000000000001</v>
+      </c>
+      <c r="G267" t="s">
+        <v>35</v>
+      </c>
+      <c r="H267" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>482</v>
+      </c>
+      <c r="B268" t="s">
+        <v>493</v>
+      </c>
+      <c r="C268" t="s">
+        <v>15</v>
+      </c>
+      <c r="D268" t="s">
+        <v>16</v>
+      </c>
+      <c r="E268">
+        <v>44.7</v>
+      </c>
+      <c r="F268">
+        <v>3</v>
+      </c>
+      <c r="G268" t="s">
+        <v>35</v>
+      </c>
+      <c r="H268" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>482</v>
+      </c>
+      <c r="B269" t="s">
+        <v>494</v>
+      </c>
+      <c r="C269" t="s">
+        <v>97</v>
+      </c>
+      <c r="D269" t="s">
+        <v>98</v>
+      </c>
+      <c r="E269">
+        <v>29.8</v>
+      </c>
+      <c r="F269">
+        <v>2</v>
+      </c>
+      <c r="G269" t="s">
+        <v>35</v>
+      </c>
+      <c r="H269" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>482</v>
+      </c>
+      <c r="B270" t="s">
+        <v>495</v>
+      </c>
+      <c r="C270" t="s">
+        <v>27</v>
+      </c>
+      <c r="D270" t="s">
+        <v>28</v>
+      </c>
+      <c r="E270">
+        <v>22.09</v>
+      </c>
+      <c r="F270">
+        <v>0.316</v>
+      </c>
+      <c r="G270" t="s">
+        <v>35</v>
+      </c>
+      <c r="H270" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>482</v>
+      </c>
+      <c r="B271" t="s">
+        <v>496</v>
+      </c>
+      <c r="C271" t="s">
+        <v>497</v>
+      </c>
+      <c r="D271" t="s">
+        <v>498</v>
+      </c>
+      <c r="E271">
+        <v>29.9</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+      <c r="G271" t="s">
+        <v>35</v>
+      </c>
+      <c r="H271" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>482</v>
+      </c>
+      <c r="B272" t="s">
+        <v>499</v>
+      </c>
+      <c r="C272" t="s">
+        <v>328</v>
+      </c>
+      <c r="D272" t="s">
+        <v>329</v>
+      </c>
+      <c r="E272">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="F272">
+        <v>2</v>
+      </c>
+      <c r="G272" t="s">
+        <v>35</v>
+      </c>
+      <c r="H272" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>482</v>
+      </c>
+      <c r="B273" t="s">
+        <v>500</v>
+      </c>
+      <c r="C273" t="s">
+        <v>12</v>
+      </c>
+      <c r="D273" t="s">
+        <v>13</v>
+      </c>
+      <c r="E273">
+        <v>0.1</v>
+      </c>
+      <c r="F273">
+        <v>5</v>
+      </c>
+      <c r="G273" t="s">
+        <v>35</v>
+      </c>
+      <c r="H273" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>482</v>
+      </c>
+      <c r="B274" t="s">
+        <v>501</v>
+      </c>
+      <c r="C274" t="s">
+        <v>87</v>
+      </c>
+      <c r="D274" t="s">
+        <v>88</v>
+      </c>
+      <c r="E274">
+        <v>47.6</v>
+      </c>
+      <c r="F274">
+        <v>4</v>
+      </c>
+      <c r="G274" t="s">
+        <v>35</v>
+      </c>
+      <c r="H274" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>482</v>
+      </c>
+      <c r="B275" t="s">
+        <v>502</v>
+      </c>
+      <c r="C275" t="s">
+        <v>59</v>
+      </c>
+      <c r="D275" t="s">
+        <v>60</v>
+      </c>
+      <c r="E275">
+        <v>43.93</v>
+      </c>
+      <c r="F275">
+        <v>7.3339999999999996</v>
+      </c>
+      <c r="G275" t="s">
+        <v>35</v>
+      </c>
+      <c r="H275" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>482</v>
+      </c>
+      <c r="B276" t="s">
+        <v>503</v>
+      </c>
+      <c r="C276" t="s">
+        <v>397</v>
+      </c>
+      <c r="D276" t="s">
+        <v>398</v>
+      </c>
+      <c r="E276">
+        <v>59.6</v>
+      </c>
+      <c r="F276">
+        <v>4</v>
+      </c>
+      <c r="G276" t="s">
+        <v>10</v>
+      </c>
+      <c r="H276" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>482</v>
+      </c>
+      <c r="B277" t="s">
+        <v>504</v>
+      </c>
+      <c r="C277" t="s">
+        <v>268</v>
+      </c>
+      <c r="D277" t="s">
+        <v>269</v>
+      </c>
+      <c r="E277">
+        <v>9.9</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+      <c r="G277" t="s">
+        <v>10</v>
+      </c>
+      <c r="H277" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>482</v>
+      </c>
+      <c r="B278" t="s">
+        <v>505</v>
+      </c>
+      <c r="C278" t="s">
+        <v>8</v>
+      </c>
+      <c r="D278" t="s">
+        <v>9</v>
+      </c>
+      <c r="E278">
+        <v>19.8</v>
+      </c>
+      <c r="F278">
+        <v>2</v>
+      </c>
+      <c r="G278" t="s">
+        <v>10</v>
+      </c>
+      <c r="H278" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>482</v>
+      </c>
+      <c r="B279" t="s">
+        <v>506</v>
+      </c>
+      <c r="C279" t="s">
+        <v>89</v>
+      </c>
+      <c r="D279" t="s">
+        <v>90</v>
+      </c>
+      <c r="E279">
+        <v>29.9</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279" t="s">
+        <v>10</v>
+      </c>
+      <c r="H279" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>482</v>
+      </c>
+      <c r="B280" t="s">
+        <v>507</v>
+      </c>
+      <c r="C280" t="s">
+        <v>132</v>
+      </c>
+      <c r="D280" t="s">
+        <v>133</v>
+      </c>
+      <c r="E280">
+        <v>48.09</v>
+      </c>
+      <c r="F280">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="G280" t="s">
+        <v>10</v>
+      </c>
+      <c r="H280" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>482</v>
+      </c>
+      <c r="B281" t="s">
+        <v>508</v>
+      </c>
+      <c r="C281" t="s">
+        <v>139</v>
+      </c>
+      <c r="D281" t="s">
+        <v>140</v>
+      </c>
+      <c r="E281">
+        <v>107.1</v>
+      </c>
+      <c r="F281">
+        <v>10.818</v>
+      </c>
+      <c r="G281" t="s">
+        <v>10</v>
+      </c>
+      <c r="H281" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>482</v>
+      </c>
+      <c r="B282" t="s">
+        <v>509</v>
+      </c>
+      <c r="C282" t="s">
+        <v>8</v>
+      </c>
+      <c r="D282" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282">
+        <v>89.1</v>
+      </c>
+      <c r="F282">
+        <v>9</v>
+      </c>
+      <c r="G282" t="s">
+        <v>10</v>
+      </c>
+      <c r="H282" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>482</v>
+      </c>
+      <c r="B283" t="s">
+        <v>510</v>
+      </c>
+      <c r="C283" t="s">
+        <v>53</v>
+      </c>
+      <c r="D283" t="s">
+        <v>54</v>
+      </c>
+      <c r="E283">
+        <v>59.5</v>
+      </c>
+      <c r="F283">
+        <v>5</v>
+      </c>
+      <c r="G283" t="s">
+        <v>10</v>
+      </c>
+      <c r="H283" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>482</v>
+      </c>
+      <c r="B284" t="s">
+        <v>511</v>
+      </c>
+      <c r="C284" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284">
+        <v>79.2</v>
+      </c>
+      <c r="F284">
+        <v>8</v>
+      </c>
+      <c r="G284" t="s">
+        <v>10</v>
+      </c>
+      <c r="H284" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>482</v>
+      </c>
+      <c r="B285" t="s">
+        <v>512</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285">
+        <v>138.6</v>
+      </c>
+      <c r="F285">
+        <v>14</v>
+      </c>
+      <c r="G285" t="s">
+        <v>10</v>
+      </c>
+      <c r="H285" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>482</v>
+      </c>
+      <c r="B286" t="s">
+        <v>513</v>
+      </c>
+      <c r="C286" t="s">
+        <v>61</v>
+      </c>
+      <c r="D286" t="s">
+        <v>62</v>
+      </c>
+      <c r="E286">
+        <v>9.9</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+      <c r="G286" t="s">
+        <v>10</v>
+      </c>
+      <c r="H286" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>482</v>
+      </c>
+      <c r="B287" t="s">
+        <v>514</v>
+      </c>
+      <c r="C287" t="s">
+        <v>179</v>
+      </c>
+      <c r="D287" t="s">
+        <v>180</v>
+      </c>
+      <c r="E287">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+      <c r="G287" t="s">
+        <v>10</v>
+      </c>
+      <c r="H287" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>482</v>
+      </c>
+      <c r="B288" t="s">
+        <v>515</v>
+      </c>
+      <c r="C288" t="s">
+        <v>36</v>
+      </c>
+      <c r="D288" t="s">
+        <v>37</v>
+      </c>
+      <c r="E288">
+        <v>29.11</v>
+      </c>
+      <c r="F288">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="G288" t="s">
+        <v>10</v>
+      </c>
+      <c r="H288" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>482</v>
+      </c>
+      <c r="B289" t="s">
+        <v>516</v>
+      </c>
+      <c r="C289" t="s">
+        <v>517</v>
+      </c>
+      <c r="D289" t="s">
+        <v>518</v>
+      </c>
+      <c r="E289">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+      <c r="G289" t="s">
+        <v>10</v>
+      </c>
+      <c r="H289" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>482</v>
+      </c>
+      <c r="B290" t="s">
+        <v>519</v>
+      </c>
+      <c r="C290" t="s">
+        <v>46</v>
+      </c>
+      <c r="D290" t="s">
+        <v>47</v>
+      </c>
+      <c r="E290">
+        <v>34.9</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290" t="s">
+        <v>10</v>
+      </c>
+      <c r="H290" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>482</v>
+      </c>
+      <c r="B291" t="s">
+        <v>520</v>
+      </c>
+      <c r="C291" t="s">
+        <v>65</v>
+      </c>
+      <c r="D291" t="s">
+        <v>66</v>
+      </c>
+      <c r="E291">
+        <v>33.71</v>
+      </c>
+      <c r="F291">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="G291" t="s">
+        <v>35</v>
+      </c>
+      <c r="H291" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>482</v>
+      </c>
+      <c r="B292" t="s">
+        <v>521</v>
+      </c>
+      <c r="C292" t="s">
+        <v>33</v>
+      </c>
+      <c r="D292" t="s">
+        <v>34</v>
+      </c>
+      <c r="E292">
+        <v>18.52</v>
+      </c>
+      <c r="F292">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="G292" t="s">
+        <v>35</v>
+      </c>
+      <c r="H292" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>482</v>
+      </c>
+      <c r="B293" t="s">
+        <v>522</v>
+      </c>
+      <c r="C293" t="s">
+        <v>81</v>
+      </c>
+      <c r="D293" t="s">
+        <v>82</v>
+      </c>
+      <c r="E293">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="F293">
+        <v>0.38</v>
+      </c>
+      <c r="G293" t="s">
+        <v>35</v>
+      </c>
+      <c r="H293" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>482</v>
+      </c>
+      <c r="B294" t="s">
+        <v>523</v>
+      </c>
+      <c r="C294" t="s">
+        <v>63</v>
+      </c>
+      <c r="D294" t="s">
+        <v>64</v>
+      </c>
+      <c r="E294">
+        <v>14.79</v>
+      </c>
+      <c r="F294">
+        <v>0.26</v>
+      </c>
+      <c r="G294" t="s">
+        <v>35</v>
+      </c>
+      <c r="H294" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>524</v>
+      </c>
+      <c r="B295" t="s">
+        <v>525</v>
+      </c>
+      <c r="C295" t="s">
+        <v>83</v>
+      </c>
+      <c r="D295" t="s">
+        <v>84</v>
+      </c>
+      <c r="E295">
+        <v>9.9</v>
+      </c>
+      <c r="F295">
+        <v>1</v>
+      </c>
+      <c r="G295" t="s">
+        <v>35</v>
+      </c>
+      <c r="H295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>524</v>
+      </c>
+      <c r="B296" t="s">
+        <v>526</v>
+      </c>
+      <c r="C296" t="s">
+        <v>527</v>
+      </c>
+      <c r="D296" t="s">
+        <v>528</v>
+      </c>
+      <c r="E296">
+        <v>26.34</v>
+      </c>
+      <c r="F296">
+        <v>0.377</v>
+      </c>
+      <c r="G296" t="s">
+        <v>35</v>
+      </c>
+      <c r="H296" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>524</v>
+      </c>
+      <c r="B297" t="s">
+        <v>529</v>
+      </c>
+      <c r="C297" t="s">
+        <v>530</v>
+      </c>
+      <c r="D297" t="s">
+        <v>531</v>
+      </c>
+      <c r="E297">
+        <v>11.72</v>
+      </c>
+      <c r="F297">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="G297" t="s">
+        <v>10</v>
+      </c>
+      <c r="H297" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>524</v>
+      </c>
+      <c r="B298" t="s">
+        <v>532</v>
+      </c>
+      <c r="C298" t="s">
+        <v>533</v>
+      </c>
+      <c r="D298" t="s">
+        <v>534</v>
+      </c>
+      <c r="E298">
+        <v>12.9</v>
+      </c>
+      <c r="F298">
+        <v>1</v>
+      </c>
+      <c r="G298" t="s">
+        <v>10</v>
+      </c>
+      <c r="H298" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>524</v>
+      </c>
+      <c r="B299" t="s">
+        <v>535</v>
+      </c>
+      <c r="C299" t="s">
+        <v>328</v>
+      </c>
+      <c r="D299" t="s">
+        <v>329</v>
+      </c>
+      <c r="E299">
+        <v>119.4</v>
+      </c>
+      <c r="F299">
+        <v>6</v>
+      </c>
+      <c r="G299" t="s">
+        <v>10</v>
+      </c>
+      <c r="H299" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>524</v>
+      </c>
+      <c r="B300" t="s">
+        <v>536</v>
+      </c>
+      <c r="C300" t="s">
+        <v>338</v>
+      </c>
+      <c r="D300" t="s">
+        <v>339</v>
+      </c>
+      <c r="E300">
+        <v>77.8</v>
+      </c>
+      <c r="F300">
+        <v>2</v>
+      </c>
+      <c r="G300" t="s">
+        <v>10</v>
+      </c>
+      <c r="H300" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>524</v>
+      </c>
+      <c r="B301" t="s">
+        <v>537</v>
+      </c>
+      <c r="C301" t="s">
+        <v>538</v>
+      </c>
+      <c r="D301" t="s">
+        <v>539</v>
+      </c>
+      <c r="E301">
+        <v>29.8</v>
+      </c>
+      <c r="F301">
+        <v>2</v>
+      </c>
+      <c r="G301" t="s">
+        <v>10</v>
+      </c>
+      <c r="H301" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>540</v>
+      </c>
+      <c r="B302" t="s">
+        <v>541</v>
+      </c>
+      <c r="C302" t="s">
+        <v>24</v>
+      </c>
+      <c r="D302" t="s">
+        <v>25</v>
+      </c>
+      <c r="E302">
+        <v>10.79</v>
+      </c>
+      <c r="F302">
+        <v>0.12</v>
+      </c>
+      <c r="G302" t="s">
+        <v>10</v>
+      </c>
+      <c r="H302" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>540</v>
+      </c>
+      <c r="B303" t="s">
+        <v>542</v>
+      </c>
+      <c r="C303" t="s">
+        <v>77</v>
+      </c>
+      <c r="D303" t="s">
+        <v>78</v>
+      </c>
+      <c r="E303">
+        <v>62.3</v>
+      </c>
+      <c r="F303">
+        <v>7</v>
+      </c>
+      <c r="G303" t="s">
+        <v>10</v>
+      </c>
+      <c r="H303" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>540</v>
+      </c>
+      <c r="B304" t="s">
+        <v>543</v>
+      </c>
+      <c r="C304" t="s">
+        <v>31</v>
+      </c>
+      <c r="D304" t="s">
+        <v>32</v>
+      </c>
+      <c r="E304">
+        <v>12.9</v>
+      </c>
+      <c r="F304">
+        <v>1</v>
+      </c>
+      <c r="G304" t="s">
+        <v>10</v>
+      </c>
+      <c r="H304" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>540</v>
+      </c>
+      <c r="B305" t="s">
+        <v>544</v>
+      </c>
+      <c r="C305" t="s">
+        <v>491</v>
+      </c>
+      <c r="D305" t="s">
+        <v>492</v>
+      </c>
+      <c r="E305">
+        <v>58.46</v>
+      </c>
+      <c r="F305">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="G305" t="s">
+        <v>10</v>
+      </c>
+      <c r="H305" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>540</v>
+      </c>
+      <c r="B306" t="s">
+        <v>545</v>
+      </c>
+      <c r="C306" t="s">
+        <v>546</v>
+      </c>
+      <c r="D306" t="s">
+        <v>547</v>
+      </c>
+      <c r="E306">
+        <v>53.55</v>
+      </c>
+      <c r="F306">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="G306" t="s">
+        <v>10</v>
+      </c>
+      <c r="H306" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>540</v>
+      </c>
+      <c r="B307" t="s">
+        <v>548</v>
+      </c>
+      <c r="C307" t="s">
+        <v>338</v>
+      </c>
+      <c r="D307" t="s">
+        <v>339</v>
+      </c>
+      <c r="E307">
+        <v>38.9</v>
+      </c>
+      <c r="F307">
+        <v>1</v>
+      </c>
+      <c r="G307" t="s">
+        <v>10</v>
+      </c>
+      <c r="H307" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>540</v>
+      </c>
+      <c r="B308" t="s">
+        <v>549</v>
+      </c>
+      <c r="C308" t="s">
+        <v>89</v>
+      </c>
+      <c r="D308" t="s">
+        <v>90</v>
+      </c>
+      <c r="E308">
+        <v>29.9</v>
+      </c>
+      <c r="F308">
+        <v>1</v>
+      </c>
+      <c r="G308" t="s">
+        <v>10</v>
+      </c>
+      <c r="H308" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>540</v>
+      </c>
+      <c r="B309" t="s">
+        <v>550</v>
+      </c>
+      <c r="C309" t="s">
+        <v>551</v>
+      </c>
+      <c r="D309" t="s">
+        <v>552</v>
+      </c>
+      <c r="E309">
+        <v>13.8</v>
+      </c>
+      <c r="F309">
+        <v>2</v>
+      </c>
+      <c r="G309" t="s">
+        <v>10</v>
+      </c>
+      <c r="H309" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>540</v>
+      </c>
+      <c r="B310" t="s">
+        <v>553</v>
+      </c>
+      <c r="C310" t="s">
+        <v>77</v>
+      </c>
+      <c r="D310" t="s">
+        <v>78</v>
+      </c>
+      <c r="E310">
+        <v>26.7</v>
+      </c>
+      <c r="F310">
+        <v>3</v>
+      </c>
+      <c r="G310" t="s">
+        <v>10</v>
+      </c>
+      <c r="H310" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>540</v>
+      </c>
+      <c r="B311" t="s">
+        <v>554</v>
+      </c>
+      <c r="C311" t="s">
+        <v>292</v>
+      </c>
+      <c r="D311" t="s">
+        <v>293</v>
+      </c>
+      <c r="E311">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="F311">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="G311" t="s">
+        <v>10</v>
+      </c>
+      <c r="H311" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>540</v>
+      </c>
+      <c r="B312" t="s">
+        <v>555</v>
+      </c>
+      <c r="C312" t="s">
+        <v>27</v>
+      </c>
+      <c r="D312" t="s">
+        <v>28</v>
+      </c>
+      <c r="E312">
+        <v>10.48</v>
+      </c>
+      <c r="F312">
+        <v>0.15</v>
+      </c>
+      <c r="G312" t="s">
+        <v>10</v>
+      </c>
+      <c r="H312" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>540</v>
+      </c>
+      <c r="B313" t="s">
+        <v>556</v>
+      </c>
+      <c r="C313" t="s">
+        <v>118</v>
+      </c>
+      <c r="D313" t="s">
+        <v>119</v>
+      </c>
+      <c r="E313">
+        <v>13.08</v>
+      </c>
+      <c r="F313">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="G313" t="s">
+        <v>10</v>
+      </c>
+      <c r="H313" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>540</v>
+      </c>
+      <c r="B314" t="s">
+        <v>557</v>
+      </c>
+      <c r="C314" t="s">
+        <v>118</v>
+      </c>
+      <c r="D314" t="s">
+        <v>119</v>
+      </c>
+      <c r="E314">
+        <v>14.59</v>
+      </c>
+      <c r="F314">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="G314" t="s">
+        <v>10</v>
+      </c>
+      <c r="H314" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>540</v>
+      </c>
+      <c r="B315" t="s">
+        <v>558</v>
+      </c>
+      <c r="C315" t="s">
+        <v>320</v>
+      </c>
+      <c r="D315" t="s">
+        <v>321</v>
+      </c>
+      <c r="E315">
+        <v>15.8</v>
+      </c>
+      <c r="F315">
+        <v>2</v>
+      </c>
+      <c r="G315" t="s">
+        <v>10</v>
+      </c>
+      <c r="H315" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>540</v>
+      </c>
+      <c r="B316" t="s">
+        <v>559</v>
+      </c>
+      <c r="C316" t="s">
+        <v>361</v>
+      </c>
+      <c r="D316" t="s">
+        <v>362</v>
+      </c>
+      <c r="E316">
+        <v>53.7</v>
+      </c>
+      <c r="F316">
+        <v>3</v>
+      </c>
+      <c r="G316" t="s">
+        <v>10</v>
+      </c>
+      <c r="H316" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>540</v>
+      </c>
+      <c r="B317" t="s">
+        <v>560</v>
+      </c>
+      <c r="C317" t="s">
+        <v>81</v>
+      </c>
+      <c r="D317" t="s">
+        <v>82</v>
+      </c>
+      <c r="E317">
+        <v>10.96</v>
+      </c>
+      <c r="F317">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="G317" t="s">
+        <v>10</v>
+      </c>
+      <c r="H317" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>540</v>
+      </c>
+      <c r="B318" t="s">
+        <v>561</v>
+      </c>
+      <c r="C318" t="s">
+        <v>33</v>
+      </c>
+      <c r="D318" t="s">
+        <v>34</v>
+      </c>
+      <c r="E318">
+        <v>34.520000000000003</v>
+      </c>
+      <c r="F318">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="G318" t="s">
+        <v>10</v>
+      </c>
+      <c r="H318" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>562</v>
+      </c>
+      <c r="B319" t="s">
+        <v>563</v>
+      </c>
+      <c r="C319" t="s">
+        <v>381</v>
+      </c>
+      <c r="D319" t="s">
+        <v>382</v>
+      </c>
+      <c r="E319">
+        <v>116.1</v>
+      </c>
+      <c r="F319">
+        <v>9</v>
+      </c>
+      <c r="G319" t="s">
+        <v>35</v>
+      </c>
+      <c r="H319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>562</v>
+      </c>
+      <c r="B320" t="s">
+        <v>564</v>
+      </c>
+      <c r="C320" t="s">
+        <v>27</v>
+      </c>
+      <c r="D320" t="s">
+        <v>28</v>
+      </c>
+      <c r="E320">
+        <v>9.23</v>
+      </c>
+      <c r="F320">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="G320" t="s">
+        <v>35</v>
+      </c>
+      <c r="H320" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>562</v>
+      </c>
+      <c r="B321" t="s">
+        <v>565</v>
+      </c>
+      <c r="C321" t="s">
+        <v>27</v>
+      </c>
+      <c r="D321" t="s">
+        <v>28</v>
+      </c>
+      <c r="E321">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="F321">
+        <v>0.122</v>
+      </c>
+      <c r="G321" t="s">
+        <v>35</v>
+      </c>
+      <c r="H321" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>562</v>
+      </c>
+      <c r="B322" t="s">
+        <v>566</v>
+      </c>
+      <c r="C322" t="s">
+        <v>89</v>
+      </c>
+      <c r="D322" t="s">
+        <v>90</v>
+      </c>
+      <c r="E322">
+        <v>29.9</v>
+      </c>
+      <c r="F322">
+        <v>1</v>
+      </c>
+      <c r="G322" t="s">
+        <v>35</v>
+      </c>
+      <c r="H322" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>562</v>
+      </c>
+      <c r="B323" t="s">
+        <v>567</v>
+      </c>
+      <c r="C323" t="s">
+        <v>36</v>
+      </c>
+      <c r="D323" t="s">
+        <v>37</v>
+      </c>
+      <c r="E323">
+        <v>270.99</v>
+      </c>
+      <c r="F323">
+        <v>4.524</v>
+      </c>
+      <c r="G323" t="s">
+        <v>35</v>
+      </c>
+      <c r="H323" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>562</v>
+      </c>
+      <c r="B324" t="s">
+        <v>568</v>
+      </c>
+      <c r="C324" t="s">
+        <v>8</v>
+      </c>
+      <c r="D324" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324">
+        <v>178.2</v>
+      </c>
+      <c r="F324">
+        <v>18</v>
+      </c>
+      <c r="G324" t="s">
+        <v>35</v>
+      </c>
+      <c r="H324" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>562</v>
+      </c>
+      <c r="B325" t="s">
+        <v>569</v>
+      </c>
+      <c r="C325" t="s">
+        <v>53</v>
+      </c>
+      <c r="D325" t="s">
+        <v>54</v>
+      </c>
+      <c r="E325">
+        <v>23.8</v>
+      </c>
+      <c r="F325">
+        <v>2</v>
+      </c>
+      <c r="G325" t="s">
+        <v>35</v>
+      </c>
+      <c r="H325" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>562</v>
+      </c>
+      <c r="B326" t="s">
+        <v>570</v>
+      </c>
+      <c r="C326" t="s">
+        <v>476</v>
+      </c>
+      <c r="D326" t="s">
+        <v>477</v>
+      </c>
+      <c r="E326">
+        <v>19.8</v>
+      </c>
+      <c r="F326">
+        <v>2</v>
+      </c>
+      <c r="G326" t="s">
+        <v>35</v>
+      </c>
+      <c r="H326" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>562</v>
+      </c>
+      <c r="B327" t="s">
+        <v>571</v>
+      </c>
+      <c r="C327" t="s">
+        <v>97</v>
+      </c>
+      <c r="D327" t="s">
+        <v>98</v>
+      </c>
+      <c r="E327">
+        <v>14.9</v>
+      </c>
+      <c r="F327">
+        <v>1</v>
+      </c>
+      <c r="G327" t="s">
+        <v>35</v>
+      </c>
+      <c r="H327" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>562</v>
+      </c>
+      <c r="B328" t="s">
+        <v>572</v>
+      </c>
+      <c r="C328" t="s">
+        <v>91</v>
+      </c>
+      <c r="D328" t="s">
+        <v>92</v>
+      </c>
+      <c r="E328">
+        <v>24.9</v>
+      </c>
+      <c r="F328">
+        <v>1</v>
+      </c>
+      <c r="G328" t="s">
+        <v>10</v>
+      </c>
+      <c r="H328" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>562</v>
+      </c>
+      <c r="B329" t="s">
+        <v>573</v>
+      </c>
+      <c r="C329" t="s">
+        <v>65</v>
+      </c>
+      <c r="D329" t="s">
+        <v>66</v>
+      </c>
+      <c r="E329">
+        <v>22.44</v>
+      </c>
+      <c r="F329">
+        <v>0.374</v>
+      </c>
+      <c r="G329" t="s">
+        <v>10</v>
+      </c>
+      <c r="H329" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>562</v>
+      </c>
+      <c r="B330" t="s">
+        <v>574</v>
+      </c>
+      <c r="C330" t="s">
+        <v>15</v>
+      </c>
+      <c r="D330" t="s">
+        <v>16</v>
+      </c>
+      <c r="E330">
+        <v>14.9</v>
+      </c>
+      <c r="F330">
+        <v>1</v>
+      </c>
+      <c r="G330" t="s">
+        <v>10</v>
+      </c>
+      <c r="H330" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>562</v>
+      </c>
+      <c r="B331" t="s">
+        <v>575</v>
+      </c>
+      <c r="C331" t="s">
+        <v>53</v>
+      </c>
+      <c r="D331" t="s">
+        <v>54</v>
+      </c>
+      <c r="E331">
+        <v>11.9</v>
+      </c>
+      <c r="F331">
+        <v>1</v>
+      </c>
+      <c r="G331" t="s">
+        <v>10</v>
+      </c>
+      <c r="H331" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>562</v>
+      </c>
+      <c r="B332" t="s">
+        <v>576</v>
+      </c>
+      <c r="C332" t="s">
+        <v>36</v>
+      </c>
+      <c r="D332" t="s">
+        <v>37</v>
+      </c>
+      <c r="E332">
+        <v>10.78</v>
+      </c>
+      <c r="F332">
+        <v>0.18</v>
+      </c>
+      <c r="G332" t="s">
+        <v>10</v>
+      </c>
+      <c r="H332" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>562</v>
+      </c>
+      <c r="B333" t="s">
+        <v>577</v>
+      </c>
+      <c r="C333" t="s">
+        <v>57</v>
+      </c>
+      <c r="D333" t="s">
+        <v>58</v>
+      </c>
+      <c r="E333">
+        <v>6.99</v>
+      </c>
+      <c r="F333">
+        <v>1</v>
+      </c>
+      <c r="G333" t="s">
+        <v>10</v>
+      </c>
+      <c r="H333" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>562</v>
+      </c>
+      <c r="B334" t="s">
+        <v>578</v>
+      </c>
+      <c r="C334" t="s">
+        <v>93</v>
+      </c>
+      <c r="D334" t="s">
+        <v>94</v>
+      </c>
+      <c r="E334">
+        <v>11.98</v>
+      </c>
+      <c r="F334">
+        <v>2</v>
+      </c>
+      <c r="G334" t="s">
+        <v>10</v>
+      </c>
+      <c r="H334" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>562</v>
+      </c>
+      <c r="B335" t="s">
+        <v>579</v>
+      </c>
+      <c r="C335" t="s">
+        <v>61</v>
+      </c>
+      <c r="D335" t="s">
+        <v>62</v>
+      </c>
+      <c r="E335">
+        <v>9.9</v>
+      </c>
+      <c r="F335">
+        <v>1</v>
+      </c>
+      <c r="G335" t="s">
+        <v>10</v>
+      </c>
+      <c r="H335" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>562</v>
+      </c>
+      <c r="B336" t="s">
+        <v>580</v>
+      </c>
+      <c r="C336" t="s">
+        <v>81</v>
+      </c>
+      <c r="D336" t="s">
+        <v>82</v>
+      </c>
+      <c r="E336">
+        <v>7.06</v>
+      </c>
+      <c r="F336">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="G336" t="s">
+        <v>10</v>
+      </c>
+      <c r="H336" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>562</v>
+      </c>
+      <c r="B337" t="s">
+        <v>581</v>
+      </c>
+      <c r="C337" t="s">
+        <v>33</v>
+      </c>
+      <c r="D337" t="s">
+        <v>34</v>
+      </c>
+      <c r="E337">
+        <v>62.93</v>
+      </c>
+      <c r="F337">
+        <v>0.7</v>
+      </c>
+      <c r="G337" t="s">
+        <v>10</v>
+      </c>
+      <c r="H337" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>582</v>
+      </c>
+      <c r="B338" t="s">
+        <v>583</v>
+      </c>
+      <c r="C338" t="s">
+        <v>114</v>
+      </c>
+      <c r="D338" t="s">
+        <v>115</v>
+      </c>
+      <c r="E338">
+        <v>29.7</v>
+      </c>
+      <c r="F338">
+        <v>3</v>
+      </c>
+      <c r="G338" t="s">
+        <v>10</v>
+      </c>
+      <c r="H338" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>582</v>
+      </c>
+      <c r="B339" t="s">
+        <v>584</v>
+      </c>
+      <c r="C339" t="s">
+        <v>111</v>
+      </c>
+      <c r="D339" t="s">
+        <v>112</v>
+      </c>
+      <c r="E339">
+        <v>27.8</v>
+      </c>
+      <c r="F339">
+        <v>2</v>
+      </c>
+      <c r="G339" t="s">
+        <v>10</v>
+      </c>
+      <c r="H339" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>582</v>
+      </c>
+      <c r="B340" t="s">
+        <v>585</v>
+      </c>
+      <c r="C340" t="s">
+        <v>44</v>
+      </c>
+      <c r="D340" t="s">
+        <v>45</v>
+      </c>
+      <c r="E340">
+        <v>29.9</v>
+      </c>
+      <c r="F340">
+        <v>1</v>
+      </c>
+      <c r="G340" t="s">
+        <v>10</v>
+      </c>
+      <c r="H340" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>582</v>
+      </c>
+      <c r="B341" t="s">
+        <v>586</v>
+      </c>
+      <c r="C341" t="s">
+        <v>163</v>
+      </c>
+      <c r="D341" t="s">
+        <v>164</v>
+      </c>
+      <c r="E341">
+        <v>26.9</v>
+      </c>
+      <c r="F341">
+        <v>1.175</v>
+      </c>
+      <c r="G341" t="s">
+        <v>10</v>
+      </c>
+      <c r="H341" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>582</v>
+      </c>
+      <c r="B342" t="s">
+        <v>587</v>
+      </c>
+      <c r="C342" t="s">
+        <v>95</v>
+      </c>
+      <c r="D342" t="s">
+        <v>96</v>
+      </c>
+      <c r="E342">
+        <v>11.48</v>
+      </c>
+      <c r="F342">
+        <v>0.23</v>
+      </c>
+      <c r="G342" t="s">
+        <v>10</v>
+      </c>
+      <c r="H342" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>582</v>
+      </c>
+      <c r="B343" t="s">
+        <v>588</v>
+      </c>
+      <c r="C343" t="s">
+        <v>12</v>
+      </c>
+      <c r="D343" t="s">
+        <v>13</v>
+      </c>
+      <c r="E343">
+        <v>17.8</v>
+      </c>
+      <c r="F343">
+        <v>2</v>
+      </c>
+      <c r="G343" t="s">
+        <v>10</v>
+      </c>
+      <c r="H343" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>582</v>
+      </c>
+      <c r="B344" t="s">
+        <v>590</v>
+      </c>
+      <c r="C344" t="s">
+        <v>27</v>
+      </c>
+      <c r="D344" t="s">
+        <v>28</v>
+      </c>
+      <c r="E344">
+        <v>8.11</v>
+      </c>
+      <c r="F344">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="G344" t="s">
+        <v>10</v>
+      </c>
+      <c r="H344" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>582</v>
+      </c>
+      <c r="B345" t="s">
+        <v>591</v>
+      </c>
+      <c r="C345" t="s">
+        <v>27</v>
+      </c>
+      <c r="D345" t="s">
+        <v>28</v>
+      </c>
+      <c r="E345">
+        <v>10.62</v>
+      </c>
+      <c r="F345">
+        <v>0.152</v>
+      </c>
+      <c r="G345" t="s">
+        <v>10</v>
+      </c>
+      <c r="H345" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>582</v>
+      </c>
+      <c r="B346" t="s">
+        <v>592</v>
+      </c>
+      <c r="C346" t="s">
+        <v>27</v>
+      </c>
+      <c r="D346" t="s">
+        <v>28</v>
+      </c>
+      <c r="E346">
+        <v>9.23</v>
+      </c>
+      <c r="F346">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="G346" t="s">
+        <v>10</v>
+      </c>
+      <c r="H346" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>582</v>
+      </c>
+      <c r="B347" t="s">
+        <v>574</v>
+      </c>
+      <c r="C347" t="s">
+        <v>27</v>
+      </c>
+      <c r="D347" t="s">
+        <v>28</v>
+      </c>
+      <c r="E347">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="F347">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G347" t="s">
+        <v>10</v>
+      </c>
+      <c r="H347" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>582</v>
+      </c>
+      <c r="B348" t="s">
+        <v>593</v>
+      </c>
+      <c r="C348" t="s">
+        <v>15</v>
+      </c>
+      <c r="D348" t="s">
+        <v>16</v>
+      </c>
+      <c r="E348">
+        <v>14.9</v>
+      </c>
+      <c r="F348">
+        <v>1</v>
+      </c>
+      <c r="G348" t="s">
+        <v>10</v>
+      </c>
+      <c r="H348" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>582</v>
+      </c>
+      <c r="B349" t="s">
+        <v>594</v>
+      </c>
+      <c r="C349" t="s">
+        <v>595</v>
+      </c>
+      <c r="D349" t="s">
+        <v>596</v>
+      </c>
+      <c r="E349">
+        <v>23.9</v>
+      </c>
+      <c r="F349">
+        <v>1</v>
+      </c>
+      <c r="G349" t="s">
+        <v>10</v>
+      </c>
+      <c r="H349" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>582</v>
+      </c>
+      <c r="B350" t="s">
+        <v>597</v>
+      </c>
+      <c r="C350" t="s">
+        <v>29</v>
+      </c>
+      <c r="D350" t="s">
+        <v>30</v>
+      </c>
+      <c r="E350">
+        <v>9.9</v>
+      </c>
+      <c r="F350">
+        <v>1</v>
+      </c>
+      <c r="G350" t="s">
+        <v>10</v>
+      </c>
+      <c r="H350" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>582</v>
+      </c>
+      <c r="B351" t="s">
+        <v>598</v>
+      </c>
+      <c r="C351" t="s">
+        <v>81</v>
+      </c>
+      <c r="D351" t="s">
+        <v>82</v>
+      </c>
+      <c r="E351">
+        <v>45.15</v>
+      </c>
+      <c r="F351">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="G351" t="s">
+        <v>10</v>
+      </c>
+      <c r="H351" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>582</v>
+      </c>
+      <c r="B352" t="s">
+        <v>599</v>
+      </c>
+      <c r="C352" t="s">
+        <v>33</v>
+      </c>
+      <c r="D352" t="s">
+        <v>34</v>
+      </c>
+      <c r="E352">
+        <v>52.5</v>
+      </c>
+      <c r="F352">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G352" t="s">
+        <v>10</v>
+      </c>
+      <c r="H352" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>600</v>
+      </c>
+      <c r="B353" t="s">
+        <v>601</v>
+      </c>
+      <c r="C353" t="s">
+        <v>331</v>
+      </c>
+      <c r="D353" t="s">
+        <v>332</v>
+      </c>
+      <c r="E353">
+        <v>8.58</v>
+      </c>
+      <c r="F353">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="G353" t="s">
+        <v>10</v>
+      </c>
+      <c r="H353" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>600</v>
+      </c>
+      <c r="B354" t="s">
+        <v>603</v>
+      </c>
+      <c r="C354" t="s">
+        <v>300</v>
+      </c>
+      <c r="D354" t="s">
+        <v>301</v>
+      </c>
+      <c r="E354">
+        <v>131.96</v>
+      </c>
+      <c r="F354">
+        <v>4.9059999999999997</v>
+      </c>
+      <c r="G354" t="s">
+        <v>10</v>
+      </c>
+      <c r="H354" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>600</v>
+      </c>
+      <c r="B355" t="s">
+        <v>604</v>
+      </c>
+      <c r="C355" t="s">
+        <v>27</v>
+      </c>
+      <c r="D355" t="s">
+        <v>28</v>
+      </c>
+      <c r="E355">
+        <v>21.53</v>
+      </c>
+      <c r="F355">
+        <v>0.308</v>
+      </c>
+      <c r="G355" t="s">
+        <v>10</v>
+      </c>
+      <c r="H355" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>600</v>
+      </c>
+      <c r="B356" t="s">
+        <v>605</v>
+      </c>
+      <c r="C356" t="s">
+        <v>44</v>
+      </c>
+      <c r="D356" t="s">
+        <v>45</v>
+      </c>
+      <c r="E356">
+        <v>59.8</v>
+      </c>
+      <c r="F356">
+        <v>2</v>
+      </c>
+      <c r="G356" t="s">
+        <v>10</v>
+      </c>
+      <c r="H356" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>600</v>
+      </c>
+      <c r="B357" t="s">
+        <v>606</v>
+      </c>
+      <c r="C357" t="s">
+        <v>607</v>
+      </c>
+      <c r="D357" t="s">
+        <v>608</v>
+      </c>
+      <c r="E357">
+        <v>169</v>
+      </c>
+      <c r="F357">
+        <v>10</v>
+      </c>
+      <c r="G357" t="s">
+        <v>10</v>
+      </c>
+      <c r="H357" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>600</v>
+      </c>
+      <c r="B358" t="s">
+        <v>609</v>
+      </c>
+      <c r="C358" t="s">
+        <v>63</v>
+      </c>
+      <c r="D358" t="s">
+        <v>64</v>
+      </c>
+      <c r="E358">
+        <v>28.22</v>
+      </c>
+      <c r="F358">
+        <v>0.496</v>
+      </c>
+      <c r="G358" t="s">
+        <v>10</v>
+      </c>
+      <c r="H358" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>600</v>
+      </c>
+      <c r="B359" t="s">
+        <v>610</v>
+      </c>
+      <c r="C359" t="s">
+        <v>611</v>
+      </c>
+      <c r="D359" t="s">
+        <v>612</v>
+      </c>
+      <c r="E359">
+        <v>69.8</v>
+      </c>
+      <c r="F359">
+        <v>4.6849999999999996</v>
+      </c>
+      <c r="G359" t="s">
+        <v>10</v>
+      </c>
+      <c r="H359" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>600</v>
+      </c>
+      <c r="B360" t="s">
+        <v>613</v>
+      </c>
+      <c r="C360" t="s">
+        <v>614</v>
+      </c>
+      <c r="D360" t="s">
+        <v>615</v>
+      </c>
+      <c r="E360">
+        <v>29.8</v>
+      </c>
+      <c r="F360">
+        <v>2</v>
+      </c>
+      <c r="G360" t="s">
+        <v>10</v>
+      </c>
+      <c r="H360" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>600</v>
+      </c>
+      <c r="B361" t="s">
+        <v>616</v>
+      </c>
+      <c r="C361" t="s">
+        <v>73</v>
+      </c>
+      <c r="D361" t="s">
+        <v>74</v>
+      </c>
+      <c r="E361">
+        <v>55.6</v>
+      </c>
+      <c r="F361">
+        <v>4</v>
+      </c>
+      <c r="G361" t="s">
+        <v>10</v>
+      </c>
+      <c r="H361" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>600</v>
+      </c>
+      <c r="B362" t="s">
+        <v>617</v>
+      </c>
+      <c r="C362" t="s">
+        <v>69</v>
+      </c>
+      <c r="D362" t="s">
+        <v>70</v>
+      </c>
+      <c r="E362">
+        <v>13.9</v>
+      </c>
+      <c r="F362">
+        <v>1</v>
+      </c>
+      <c r="G362" t="s">
+        <v>10</v>
+      </c>
+      <c r="H362" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>600</v>
+      </c>
+      <c r="B363" t="s">
+        <v>618</v>
+      </c>
+      <c r="C363" t="s">
+        <v>619</v>
+      </c>
+      <c r="D363" t="s">
+        <v>620</v>
+      </c>
+      <c r="E363">
+        <v>20.96</v>
+      </c>
+      <c r="F363">
+        <v>0.35</v>
+      </c>
+      <c r="G363" t="s">
+        <v>10</v>
+      </c>
+      <c r="H363" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>600</v>
+      </c>
+      <c r="B364" t="s">
+        <v>621</v>
+      </c>
+      <c r="C364" t="s">
+        <v>527</v>
+      </c>
+      <c r="D364" t="s">
+        <v>528</v>
+      </c>
+      <c r="E364">
+        <v>14.82</v>
+      </c>
+      <c r="F364">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="G364" t="s">
+        <v>10</v>
+      </c>
+      <c r="H364" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>600</v>
+      </c>
+      <c r="B365" t="s">
+        <v>622</v>
+      </c>
+      <c r="C365" t="s">
+        <v>623</v>
+      </c>
+      <c r="D365" t="s">
+        <v>624</v>
+      </c>
+      <c r="E365">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="F365">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="G365" t="s">
+        <v>10</v>
+      </c>
+      <c r="H365" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>600</v>
+      </c>
+      <c r="B366" t="s">
+        <v>625</v>
+      </c>
+      <c r="C366" t="s">
+        <v>33</v>
+      </c>
+      <c r="D366" t="s">
+        <v>34</v>
+      </c>
+      <c r="E366">
+        <v>21.58</v>
+      </c>
+      <c r="F366">
+        <v>0.24</v>
+      </c>
+      <c r="G366" t="s">
+        <v>10</v>
+      </c>
+      <c r="H366" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>600</v>
+      </c>
+      <c r="B367" t="s">
+        <v>626</v>
+      </c>
+      <c r="C367" t="s">
+        <v>81</v>
+      </c>
+      <c r="D367" t="s">
+        <v>82</v>
+      </c>
+      <c r="E367">
+        <v>21.74</v>
+      </c>
+      <c r="F367">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="G367" t="s">
+        <v>10</v>
+      </c>
+      <c r="H367" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>627</v>
+      </c>
+      <c r="B368" t="s">
+        <v>628</v>
+      </c>
+      <c r="C368" t="s">
+        <v>107</v>
+      </c>
+      <c r="D368" t="s">
+        <v>108</v>
+      </c>
+      <c r="E368">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F368">
+        <v>1</v>
+      </c>
+      <c r="G368" t="s">
+        <v>10</v>
+      </c>
+      <c r="H368" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>627</v>
+      </c>
+      <c r="B369" t="s">
+        <v>629</v>
+      </c>
+      <c r="C369" t="s">
+        <v>393</v>
+      </c>
+      <c r="D369" t="s">
+        <v>394</v>
+      </c>
+      <c r="E369">
+        <v>14.9</v>
+      </c>
+      <c r="F369">
+        <v>1</v>
+      </c>
+      <c r="G369" t="s">
+        <v>10</v>
+      </c>
+      <c r="H369" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>627</v>
+      </c>
+      <c r="B370" t="s">
+        <v>630</v>
+      </c>
+      <c r="C370" t="s">
+        <v>631</v>
+      </c>
+      <c r="D370" t="s">
+        <v>632</v>
+      </c>
+      <c r="E370">
+        <v>64.5</v>
+      </c>
+      <c r="F370">
+        <v>5</v>
+      </c>
+      <c r="G370" t="s">
+        <v>10</v>
+      </c>
+      <c r="H370" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>627</v>
+      </c>
+      <c r="B371" t="s">
+        <v>633</v>
+      </c>
+      <c r="C371" t="s">
+        <v>125</v>
+      </c>
+      <c r="D371" t="s">
+        <v>126</v>
+      </c>
+      <c r="E371">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="F371">
+        <v>2</v>
+      </c>
+      <c r="G371" t="s">
+        <v>10</v>
+      </c>
+      <c r="H371" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>627</v>
+      </c>
+      <c r="B372" t="s">
+        <v>634</v>
+      </c>
+      <c r="C372" t="s">
+        <v>27</v>
+      </c>
+      <c r="D372" t="s">
+        <v>28</v>
+      </c>
+      <c r="E372">
+        <v>23.77</v>
+      </c>
+      <c r="F372">
+        <v>0.34</v>
+      </c>
+      <c r="G372" t="s">
+        <v>10</v>
+      </c>
+      <c r="H372" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>627</v>
+      </c>
+      <c r="B373" t="s">
+        <v>635</v>
+      </c>
+      <c r="C373" t="s">
+        <v>538</v>
+      </c>
+      <c r="D373" t="s">
+        <v>539</v>
+      </c>
+      <c r="E373">
+        <v>14.9</v>
+      </c>
+      <c r="F373">
+        <v>1</v>
+      </c>
+      <c r="G373" t="s">
+        <v>10</v>
+      </c>
+      <c r="H373" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>627</v>
+      </c>
+      <c r="B374" t="s">
+        <v>637</v>
+      </c>
+      <c r="C374" t="s">
+        <v>538</v>
+      </c>
+      <c r="D374" t="s">
+        <v>539</v>
+      </c>
+      <c r="E374">
+        <v>14.9</v>
+      </c>
+      <c r="F374">
+        <v>1</v>
+      </c>
+      <c r="G374" t="s">
+        <v>10</v>
+      </c>
+      <c r="H374" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>627</v>
+      </c>
+      <c r="B375" t="s">
+        <v>638</v>
+      </c>
+      <c r="C375" t="s">
+        <v>57</v>
+      </c>
+      <c r="D375" t="s">
+        <v>58</v>
+      </c>
+      <c r="E375">
+        <v>34.950000000000003</v>
+      </c>
+      <c r="F375">
+        <v>5</v>
+      </c>
+      <c r="G375" t="s">
+        <v>10</v>
+      </c>
+      <c r="H375" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>627</v>
+      </c>
+      <c r="B376" t="s">
+        <v>639</v>
+      </c>
+      <c r="C376" t="s">
+        <v>39</v>
+      </c>
+      <c r="D376" t="s">
+        <v>40</v>
+      </c>
+      <c r="E376">
+        <v>39.6</v>
+      </c>
+      <c r="F376">
+        <v>4</v>
+      </c>
+      <c r="G376" t="s">
+        <v>10</v>
+      </c>
+      <c r="H376" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>627</v>
+      </c>
+      <c r="B377" t="s">
+        <v>640</v>
+      </c>
+      <c r="C377" t="s">
+        <v>59</v>
+      </c>
+      <c r="D377" t="s">
+        <v>60</v>
+      </c>
+      <c r="E377">
+        <v>41.93</v>
+      </c>
+      <c r="F377">
+        <v>7</v>
+      </c>
+      <c r="G377" t="s">
+        <v>10</v>
+      </c>
+      <c r="H377" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>627</v>
+      </c>
+      <c r="B378" t="s">
+        <v>641</v>
+      </c>
+      <c r="C378" t="s">
+        <v>12</v>
+      </c>
+      <c r="D378" t="s">
+        <v>13</v>
+      </c>
+      <c r="E378">
+        <v>62.3</v>
+      </c>
+      <c r="F378">
+        <v>7</v>
+      </c>
+      <c r="G378" t="s">
+        <v>10</v>
+      </c>
+      <c r="H378" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>627</v>
+      </c>
+      <c r="B379" t="s">
+        <v>642</v>
+      </c>
+      <c r="C379" t="s">
+        <v>29</v>
+      </c>
+      <c r="D379" t="s">
+        <v>30</v>
+      </c>
+      <c r="E379">
+        <v>19.8</v>
+      </c>
+      <c r="F379">
+        <v>2</v>
+      </c>
+      <c r="G379" t="s">
+        <v>10</v>
+      </c>
+      <c r="H379" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
